--- a/Chei5.xlsx
+++ b/Chei5.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="14">
   <si>
     <t>Description</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>bankily</t>
+  </si>
+  <si>
+    <t>Cart apple</t>
   </si>
 </sst>
 </file>
@@ -120,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -137,13 +140,46 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -440,73 +476,109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:M29"/>
+  <dimension ref="B2:U29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.5703125" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="16384" width="17.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="24" customHeight="1">
-      <c r="B2" s="7">
+    <row r="2" spans="2:21" ht="24" customHeight="1">
+      <c r="B2" s="17">
         <v>11</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="18">
         <f>SUM(D5:D31)</f>
         <v>2750</v>
       </c>
-      <c r="D2" s="8"/>
-      <c r="F2" s="7">
+      <c r="D2" s="18"/>
+      <c r="F2" s="17">
         <v>12</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="18">
         <f>SUM(H21-I21)</f>
         <v>12570</v>
       </c>
-      <c r="H2" s="8"/>
-      <c r="K2" s="7">
+      <c r="H2" s="18"/>
+      <c r="K2" s="17">
         <v>1</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="18">
         <f>SUM(M$5:M$1048576)</f>
         <v>600</v>
       </c>
-      <c r="M2" s="8"/>
-    </row>
-    <row r="3" spans="2:13" ht="24" customHeight="1">
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-    </row>
-    <row r="4" spans="2:13" ht="24" customHeight="1">
-      <c r="B4" s="7"/>
+      <c r="M2" s="18"/>
+      <c r="O2" s="17">
+        <v>2</v>
+      </c>
+      <c r="P2" s="18">
+        <f>SUM(Q$5:Q$1048576)</f>
+        <v>4850</v>
+      </c>
+      <c r="Q2" s="18"/>
+      <c r="S2" s="17">
+        <v>3</v>
+      </c>
+      <c r="T2" s="18">
+        <f>SUM(U$5:U$1048576)</f>
+        <v>6980</v>
+      </c>
+      <c r="U2" s="18"/>
+    </row>
+    <row r="3" spans="2:21" ht="24" customHeight="1">
+      <c r="B3" s="17"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="18"/>
+      <c r="U3" s="18"/>
+    </row>
+    <row r="4" spans="2:21" ht="24" customHeight="1">
+      <c r="B4" s="17"/>
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="7"/>
+      <c r="F4" s="17"/>
       <c r="G4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="7"/>
+      <c r="K4" s="17"/>
       <c r="L4" s="4" t="s">
         <v>0</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="2:13" ht="24" customHeight="1">
+      <c r="O4" s="17"/>
+      <c r="P4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="17"/>
+      <c r="T4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="U4" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" ht="24" customHeight="1">
       <c r="B5" s="3">
         <v>45962</v>
       </c>
@@ -534,8 +606,26 @@
       <c r="M5" s="1">
         <v>300</v>
       </c>
-    </row>
-    <row r="6" spans="2:13" ht="24" customHeight="1">
+      <c r="O5" s="3">
+        <v>46054</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>250</v>
+      </c>
+      <c r="S5" s="3">
+        <v>46093</v>
+      </c>
+      <c r="T5" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="U5" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" ht="24" customHeight="1">
       <c r="B6" s="3">
         <v>45965</v>
       </c>
@@ -563,8 +653,26 @@
       <c r="M6" s="1">
         <v>300</v>
       </c>
-    </row>
-    <row r="7" spans="2:13" ht="24" customHeight="1">
+      <c r="O6" s="3">
+        <v>46073</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>300</v>
+      </c>
+      <c r="S6" s="3">
+        <v>46095</v>
+      </c>
+      <c r="T6" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="U6" s="12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21" ht="24" customHeight="1">
       <c r="B7" s="3">
         <v>45966</v>
       </c>
@@ -583,8 +691,26 @@
       <c r="H7" s="1">
         <v>5000</v>
       </c>
-    </row>
-    <row r="8" spans="2:13" ht="24" customHeight="1">
+      <c r="O7" s="3">
+        <v>46073</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>2000</v>
+      </c>
+      <c r="S7" s="3">
+        <v>46100</v>
+      </c>
+      <c r="T7" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="1">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21" ht="24" customHeight="1">
       <c r="B8" s="3">
         <v>45967</v>
       </c>
@@ -603,8 +729,26 @@
       <c r="H8" s="1">
         <v>300</v>
       </c>
-    </row>
-    <row r="9" spans="2:13" ht="24" customHeight="1">
+      <c r="O8" s="3">
+        <v>46077</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>300</v>
+      </c>
+      <c r="S8" s="3">
+        <v>46102</v>
+      </c>
+      <c r="T8" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="U8" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21" ht="24" customHeight="1">
       <c r="B9" s="3">
         <v>45968</v>
       </c>
@@ -623,8 +767,26 @@
       <c r="H9" s="1">
         <v>200</v>
       </c>
-    </row>
-    <row r="10" spans="2:13" ht="24" customHeight="1">
+      <c r="O9" s="3">
+        <v>46082</v>
+      </c>
+      <c r="P9" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>2000</v>
+      </c>
+      <c r="S9" s="3">
+        <v>46105</v>
+      </c>
+      <c r="T9" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="U9" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21" ht="24" customHeight="1">
       <c r="B10" s="3">
         <v>45969</v>
       </c>
@@ -643,8 +805,17 @@
       <c r="H10" s="1">
         <v>1000</v>
       </c>
-    </row>
-    <row r="11" spans="2:13" ht="24" customHeight="1">
+      <c r="S10" s="3">
+        <v>46109</v>
+      </c>
+      <c r="T10" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="U10" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21" ht="24" customHeight="1">
       <c r="B11" s="3">
         <v>45972</v>
       </c>
@@ -663,8 +834,17 @@
       <c r="H11" s="1">
         <v>200</v>
       </c>
-    </row>
-    <row r="12" spans="2:13" ht="24" customHeight="1">
+      <c r="S11" s="3">
+        <v>46109</v>
+      </c>
+      <c r="T11" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="U11" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21" ht="24" customHeight="1">
       <c r="B12" s="3">
         <v>45974</v>
       </c>
@@ -683,8 +863,17 @@
       <c r="H12" s="1">
         <v>5000</v>
       </c>
-    </row>
-    <row r="13" spans="2:13" ht="24" customHeight="1">
+      <c r="S12" s="3">
+        <v>46110</v>
+      </c>
+      <c r="T12" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="U12" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21" ht="24" customHeight="1">
       <c r="B13" s="3">
         <v>45975</v>
       </c>
@@ -704,7 +893,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="14" spans="2:13" ht="24" customHeight="1">
+    <row r="14" spans="2:21" ht="24" customHeight="1">
       <c r="B14" s="3">
         <v>45976</v>
       </c>
@@ -724,7 +913,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="2:13" ht="24" customHeight="1">
+    <row r="15" spans="2:21" ht="24" customHeight="1">
       <c r="B15" s="3">
         <v>45978</v>
       </c>
@@ -744,7 +933,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="16" spans="2:13" ht="24" customHeight="1">
+    <row r="16" spans="2:21" ht="24" customHeight="1">
       <c r="B16" s="3">
         <v>45980</v>
       </c>
@@ -821,14 +1010,14 @@
       <c r="D21" s="1">
         <v>100</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="19">
         <f>SUM(H5:H20)</f>
         <v>15470</v>
       </c>
-      <c r="I21" s="6">
+      <c r="I21" s="19">
         <f>SUM(I16:I20)</f>
         <v>2900</v>
       </c>
@@ -843,9 +1032,9 @@
       <c r="D22" s="1">
         <v>250</v>
       </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
     </row>
     <row r="23" spans="2:9" ht="21">
       <c r="B23" s="3">
@@ -893,9 +1082,7 @@
       <c r="B29" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:M3"/>
+  <mergeCells count="13">
     <mergeCell ref="I21:I22"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="B2:B4"/>
@@ -903,6 +1090,12 @@
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="G2:H3"/>
     <mergeCell ref="H21:H22"/>
+    <mergeCell ref="S2:S4"/>
+    <mergeCell ref="T2:U3"/>
+    <mergeCell ref="O2:O4"/>
+    <mergeCell ref="P2:Q3"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>

--- a/Chei5.xlsx
+++ b/Chei5.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="15">
   <si>
     <t>Description</t>
   </si>
@@ -58,13 +58,16 @@
   </si>
   <si>
     <t>Cart apple</t>
+  </si>
+  <si>
+    <t>adobe</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,6 +86,13 @@
       <b/>
       <sz val="16"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -123,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -173,13 +183,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -476,109 +501,127 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:U29"/>
+  <dimension ref="B2:Y29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.5703125" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="16384" width="17.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" ht="24" customHeight="1">
-      <c r="B2" s="17">
+    <row r="2" spans="2:25" ht="24" customHeight="1">
+      <c r="B2" s="23">
         <v>11</v>
       </c>
-      <c r="C2" s="18">
+      <c r="C2" s="24">
         <f>SUM(D5:D31)</f>
         <v>2750</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="F2" s="17">
+      <c r="D2" s="24"/>
+      <c r="F2" s="23">
         <v>12</v>
       </c>
-      <c r="G2" s="18">
+      <c r="G2" s="24">
         <f>SUM(H21-I21)</f>
         <v>12570</v>
       </c>
-      <c r="H2" s="18"/>
-      <c r="K2" s="17">
+      <c r="H2" s="24"/>
+      <c r="K2" s="23">
         <v>1</v>
       </c>
-      <c r="L2" s="18">
+      <c r="L2" s="24">
         <f>SUM(M$5:M$1048576)</f>
         <v>600</v>
       </c>
-      <c r="M2" s="18"/>
-      <c r="O2" s="17">
-        <v>2</v>
-      </c>
-      <c r="P2" s="18">
+      <c r="M2" s="24"/>
+      <c r="O2" s="23">
+        <v>2</v>
+      </c>
+      <c r="P2" s="24">
         <f>SUM(Q$5:Q$1048576)</f>
         <v>4850</v>
       </c>
-      <c r="Q2" s="18"/>
-      <c r="S2" s="17">
+      <c r="Q2" s="24"/>
+      <c r="S2" s="23">
         <v>3</v>
       </c>
-      <c r="T2" s="18">
+      <c r="T2" s="24">
         <f>SUM(U$5:U$1048576)</f>
-        <v>6980</v>
-      </c>
-      <c r="U2" s="18"/>
-    </row>
-    <row r="3" spans="2:21" ht="24" customHeight="1">
-      <c r="B3" s="17"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="18"/>
-      <c r="Q3" s="18"/>
-      <c r="S3" s="17"/>
-      <c r="T3" s="18"/>
-      <c r="U3" s="18"/>
-    </row>
-    <row r="4" spans="2:21" ht="24" customHeight="1">
-      <c r="B4" s="17"/>
+        <v>10280</v>
+      </c>
+      <c r="U2" s="24"/>
+      <c r="W2" s="23">
+        <v>4</v>
+      </c>
+      <c r="X2" s="24">
+        <f>SUM(Y$5:Y$1048576)</f>
+        <v>200</v>
+      </c>
+      <c r="Y2" s="24"/>
+    </row>
+    <row r="3" spans="2:25" ht="24" customHeight="1">
+      <c r="B3" s="23"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="24"/>
+      <c r="U3" s="24"/>
+      <c r="W3" s="23"/>
+      <c r="X3" s="24"/>
+      <c r="Y3" s="24"/>
+    </row>
+    <row r="4" spans="2:25" ht="24" customHeight="1">
+      <c r="B4" s="23"/>
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="17"/>
+      <c r="F4" s="23"/>
       <c r="G4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="17"/>
+      <c r="K4" s="23"/>
       <c r="L4" s="4" t="s">
         <v>0</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="17"/>
+      <c r="O4" s="23"/>
       <c r="P4" s="6" t="s">
         <v>0</v>
       </c>
       <c r="Q4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="S4" s="17"/>
+      <c r="S4" s="23"/>
       <c r="T4" s="11" t="s">
         <v>0</v>
       </c>
       <c r="U4" s="11" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="2:21" ht="24" customHeight="1">
+      <c r="W4" s="23"/>
+      <c r="X4" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="19" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:25" ht="24" customHeight="1">
       <c r="B5" s="3">
         <v>45962</v>
       </c>
@@ -624,8 +667,17 @@
       <c r="U5" s="1">
         <v>200</v>
       </c>
-    </row>
-    <row r="6" spans="2:21" ht="24" customHeight="1">
+      <c r="W5" s="3">
+        <v>46120</v>
+      </c>
+      <c r="X5" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="2:25" ht="24" customHeight="1">
       <c r="B6" s="3">
         <v>45965</v>
       </c>
@@ -672,7 +724,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="2:21" ht="24" customHeight="1">
+    <row r="7" spans="2:25" ht="24" customHeight="1">
       <c r="B7" s="3">
         <v>45966</v>
       </c>
@@ -706,11 +758,11 @@
       <c r="T7" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="U7" s="1">
+      <c r="U7" s="21">
         <v>-900</v>
       </c>
     </row>
-    <row r="8" spans="2:21" ht="24" customHeight="1">
+    <row r="8" spans="2:25" ht="24" customHeight="1">
       <c r="B8" s="3">
         <v>45967</v>
       </c>
@@ -748,7 +800,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="9" spans="2:21" ht="24" customHeight="1">
+    <row r="9" spans="2:25" ht="24" customHeight="1">
       <c r="B9" s="3">
         <v>45968</v>
       </c>
@@ -786,7 +838,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="10" spans="2:21" ht="24" customHeight="1">
+    <row r="10" spans="2:25" ht="24" customHeight="1">
       <c r="B10" s="3">
         <v>45969</v>
       </c>
@@ -815,7 +867,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="2:21" ht="24" customHeight="1">
+    <row r="11" spans="2:25" ht="24" customHeight="1">
       <c r="B11" s="3">
         <v>45972</v>
       </c>
@@ -844,7 +896,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="12" spans="2:21" ht="24" customHeight="1">
+    <row r="12" spans="2:25" ht="24" customHeight="1">
       <c r="B12" s="3">
         <v>45974</v>
       </c>
@@ -873,7 +925,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="2:21" ht="24" customHeight="1">
+    <row r="13" spans="2:25" ht="24" customHeight="1">
       <c r="B13" s="3">
         <v>45975</v>
       </c>
@@ -892,8 +944,17 @@
       <c r="H13" s="1">
         <v>110</v>
       </c>
-    </row>
-    <row r="14" spans="2:21" ht="24" customHeight="1">
+      <c r="S13" s="3">
+        <v>46111</v>
+      </c>
+      <c r="T13" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="U13" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:25" ht="24" customHeight="1">
       <c r="B14" s="3">
         <v>45976</v>
       </c>
@@ -912,8 +973,17 @@
       <c r="H14" s="1">
         <v>60</v>
       </c>
-    </row>
-    <row r="15" spans="2:21" ht="24" customHeight="1">
+      <c r="S14" s="3">
+        <v>46096</v>
+      </c>
+      <c r="T14" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="U14" s="21">
+        <v>-350</v>
+      </c>
+    </row>
+    <row r="15" spans="2:25" ht="24" customHeight="1">
       <c r="B15" s="3">
         <v>45978</v>
       </c>
@@ -932,8 +1002,17 @@
       <c r="H15" s="1">
         <v>3400</v>
       </c>
-    </row>
-    <row r="16" spans="2:21" ht="24" customHeight="1">
+      <c r="S15" s="3">
+        <v>46095</v>
+      </c>
+      <c r="T15" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="U15" s="21">
+        <v>-1350</v>
+      </c>
+    </row>
+    <row r="16" spans="2:25" ht="24" customHeight="1">
       <c r="B16" s="3">
         <v>45980</v>
       </c>
@@ -1010,14 +1089,14 @@
       <c r="D21" s="1">
         <v>100</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="19">
+      <c r="H21" s="22">
         <f>SUM(H5:H20)</f>
         <v>15470</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="22">
         <f>SUM(I16:I20)</f>
         <v>2900</v>
       </c>
@@ -1032,9 +1111,9 @@
       <c r="D22" s="1">
         <v>250</v>
       </c>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
     </row>
     <row r="23" spans="2:9" ht="21">
       <c r="B23" s="3">
@@ -1082,7 +1161,15 @@
       <c r="B29" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
+    <mergeCell ref="W2:W4"/>
+    <mergeCell ref="X2:Y3"/>
+    <mergeCell ref="S2:S4"/>
+    <mergeCell ref="T2:U3"/>
+    <mergeCell ref="O2:O4"/>
+    <mergeCell ref="P2:Q3"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:M3"/>
     <mergeCell ref="I21:I22"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="B2:B4"/>
@@ -1090,15 +1177,9 @@
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="G2:H3"/>
     <mergeCell ref="H21:H22"/>
-    <mergeCell ref="S2:S4"/>
-    <mergeCell ref="T2:U3"/>
-    <mergeCell ref="O2:O4"/>
-    <mergeCell ref="P2:Q3"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
